--- a/ig/ch-elm/StructureDefinition-ch-elm-servicerequest-previous-laboratory-order.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-servicerequest-previous-laboratory-order.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -371,7 +371,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -547,7 +547,7 @@
     <t>dataabsentreason</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {data-absent-reason}
+    <t xml:space="preserve">Extension {data-absent-reason|5.3.0}
 </t>
   </si>
   <si>
@@ -725,7 +725,7 @@
     <t>ServiceRequest.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ActivityDefinition|PlanDefinition)
+    <t xml:space="preserve">canonical(ActivityDefinition|4.0.1|PlanDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -769,7 +769,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest|MedicationRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1|MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -795,7 +795,7 @@
 priorrenewed order</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -929,7 +929,7 @@
     <t>Classification of the requested service.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-category|4.0.1</t>
   </si>
   <si>
     <t>RF1-5</t>
@@ -1049,7 +1049,7 @@
     <t>Codified order entry details which are based on order context.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail</t>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">prr-1
@@ -1113,7 +1113,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1186,7 +1186,7 @@
     <t>A coded concept identifying the pre-condition that should hold prior to performing a procedure.  For example "pain", "on flare-up", etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason|4.0.1</t>
   </si>
   <si>
     <t>boolean: precondition.negationInd (inversed - so negationInd = true means asNeeded=false CodeableConcept: precondition.observationEventCriterion[code="Assertion"].value</t>
@@ -1281,7 +1281,7 @@
     <t>Indicates specific responsibility of an individual within the care team, such as "Primary physician", "Team coordinator", "Caregiver", etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/participant-role</t>
+    <t>http://hl7.org/fhir/ValueSet/participant-role|4.0.1</t>
   </si>
   <si>
     <t>Request.performerType</t>
@@ -1303,7 +1303,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|HealthcareService|Patient|Device|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|HealthcareService|4.0.1|Patient|4.0.1|Device|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1337,7 +1337,7 @@
     <t>A location type where services are delivered.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType|3.0.0</t>
   </si>
   <si>
     <t>.participation[typeCode=LOC].role[scoper.determinerCode=KIND].code</t>
@@ -1346,7 +1346,7 @@
     <t>ServiceRequest.locationReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1371,7 +1371,7 @@
     <t>Diagnosis or problem codes justifying the reason for requesting the service investigation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1389,7 +1389,7 @@
     <t>ServiceRequest.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport|DocumentReference)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
 </t>
   </si>
   <si>
@@ -1440,7 +1440,7 @@
 AOE</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1508,7 +1508,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>targetSiteCode</t>
@@ -1551,7 +1551,7 @@
     <t>ServiceRequest.relevantHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -1886,7 +1886,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="90.37890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="126.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1901,7 +1901,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="108.3203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="58.125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.65234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/ig/ch-elm/StructureDefinition-ch-elm-servicerequest-previous-laboratory-order.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-servicerequest-previous-laboratory-order.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-servicerequest-previous-laboratory-order.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-servicerequest-previous-laboratory-order.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-servicerequest-previous-laboratory-order.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-servicerequest-previous-laboratory-order.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
